--- a/docs/StructureDefinition-DIPSPerson.xlsx
+++ b/docs/StructureDefinition-DIPSPerson.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:16:58+00:00</t>
+    <t>2026-09-08T11:30:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -761,7 +761,7 @@
     <t>language</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPersonLanguage}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPersonLanguage}
 </t>
   </si>
   <si>
@@ -802,7 +802,7 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPersonLanguage</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPersonLanguage</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -880,7 +880,7 @@
     <t>deathRegisteredTime</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPersonDeathRegisteredTime}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPersonDeathRegisteredTime}
 </t>
   </si>
   <si>
@@ -890,7 +890,7 @@
     <t>deathComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPersonDeathComment}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPersonDeathComment}
 </t>
   </si>
   <si>
@@ -900,7 +900,7 @@
     <t>deathRegisteredBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPersonDeathRegisteredBy}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPersonDeathRegisteredBy}
 </t>
   </si>
   <si>
@@ -910,7 +910,7 @@
     <t>hospitalSectorId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPersonHospitalSectorId}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPersonHospitalSectorId}
 </t>
   </si>
   <si>
@@ -920,7 +920,7 @@
     <t>hospitalSectorName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPersonHospitalSectorName}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPersonHospitalSectorName}
 </t>
   </si>
   <si>
@@ -1651,7 +1651,7 @@
     <t>stateName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPersonStateName}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPersonStateName}
 </t>
   </si>
   <si>
@@ -1661,7 +1661,7 @@
     <t>lastOfficialAddressSyncTime</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPersonLastOfficialAddressSyncTime}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPersonLastOfficialAddressSyncTime}
 </t>
   </si>
   <si>
@@ -1856,7 +1856,7 @@
     <t>muniplaity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPersonMunicipality}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPersonMunicipality}
 </t>
   </si>
   <si>
@@ -1878,7 +1878,7 @@
     <t>Person.address.district.extension.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPersonMunicipality</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPersonMunicipality</t>
   </si>
   <si>
     <t>Person.address.district.extension:muniplaity.value[x]</t>

--- a/docs/StructureDefinition-DIPSPerson.xlsx
+++ b/docs/StructureDefinition-DIPSPerson.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:30:20+00:00</t>
+    <t>2026-09-15T05:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPerson.xlsx
+++ b/docs/StructureDefinition-DIPSPerson.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4930" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4930" uniqueCount="712">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T05:06:55+00:00</t>
+    <t>2026-09-17T19:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1310,6 +1310,10 @@
     <t>middlename</t>
   </si>
   <si>
+    <t xml:space="preserve">mellomnavn
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension {http://hl7.no/fhir/StructureDefinition/no-basis-middlename}
 </t>
   </si>
@@ -1617,6 +1621,10 @@
   </si>
   <si>
     <t>urbanDistrict</t>
+  </si>
+  <si>
+    <t>bydel
+urban district</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://hl7.no/fhir/StructureDefinition/no-basis-urban-district}
@@ -11694,14 +11702,14 @@
         <v>417</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>74</v>
+        <v>418</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>74</v>
@@ -11713,13 +11721,13 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11796,10 +11804,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11825,16 +11833,16 @@
         <v>173</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>74</v>
@@ -11862,10 +11870,10 @@
         <v>314</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>74</v>
@@ -11883,7 +11891,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
@@ -11898,21 +11906,21 @@
         <v>96</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11938,16 +11946,16 @@
         <v>98</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>74</v>
@@ -11996,7 +12004,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
@@ -12011,25 +12019,25 @@
         <v>96</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12051,13 +12059,13 @@
         <v>98</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12107,7 +12115,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
@@ -12122,25 +12130,25 @@
         <v>96</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12162,13 +12170,13 @@
         <v>98</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12218,7 +12226,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>75</v>
@@ -12233,21 +12241,21 @@
         <v>96</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12273,10 +12281,10 @@
         <v>98</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12327,7 +12335,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
@@ -12342,21 +12350,21 @@
         <v>96</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12382,10 +12390,10 @@
         <v>98</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12436,7 +12444,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -12451,21 +12459,21 @@
         <v>96</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12491,14 +12499,14 @@
         <v>347</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>74</v>
@@ -12547,7 +12555,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
@@ -12562,21 +12570,21 @@
         <v>96</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12599,19 +12607,19 @@
         <v>85</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>74</v>
@@ -12660,7 +12668,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
@@ -12675,21 +12683,21 @@
         <v>96</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12715,16 +12723,16 @@
         <v>173</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>74</v>
@@ -12752,10 +12760,10 @@
         <v>314</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>74</v>
@@ -12773,7 +12781,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>
@@ -12788,21 +12796,21 @@
         <v>96</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12825,19 +12833,19 @@
         <v>85</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>74</v>
@@ -12886,7 +12894,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>75</v>
@@ -12901,21 +12909,21 @@
         <v>96</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12938,19 +12946,19 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>74</v>
@@ -12999,7 +13007,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -13014,21 +13022,21 @@
         <v>96</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13057,7 +13065,7 @@
         <v>99</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13134,10 +13142,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13243,13 +13251,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="B97" t="s" s="2">
-        <v>509</v>
-      </c>
       <c r="C97" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>74</v>
@@ -13259,7 +13267,7 @@
         <v>75</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>74</v>
@@ -13271,13 +13279,13 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13354,16 +13362,16 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>74</v>
+        <v>518</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13382,13 +13390,13 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13465,13 +13473,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>74</v>
@@ -13493,13 +13501,13 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13576,13 +13584,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>74</v>
@@ -13604,7 +13612,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>242</v>
@@ -13687,13 +13695,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>74</v>
@@ -13715,7 +13723,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L101" t="s" s="2">
         <v>242</v>
@@ -13798,10 +13806,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13827,16 +13835,16 @@
         <v>173</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>74</v>
@@ -13849,7 +13857,7 @@
         <v>74</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>74</v>
@@ -13864,10 +13872,10 @@
         <v>314</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>74</v>
@@ -13885,7 +13893,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
@@ -13900,21 +13908,21 @@
         <v>96</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13940,13 +13948,13 @@
         <v>173</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13960,7 +13968,7 @@
         <v>74</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>74</v>
@@ -13975,10 +13983,10 @@
         <v>314</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>74</v>
@@ -13996,7 +14004,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>75</v>
@@ -14011,21 +14019,21 @@
         <v>96</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14051,16 +14059,16 @@
         <v>98</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>74</v>
@@ -14073,7 +14081,7 @@
         <v>74</v>
       </c>
       <c r="T104" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="U104" t="s" s="2">
         <v>74</v>
@@ -14109,7 +14117,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -14124,21 +14132,21 @@
         <v>96</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14164,10 +14172,10 @@
         <v>98</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14182,7 +14190,7 @@
         <v>74</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>74</v>
@@ -14218,7 +14226,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>75</v>
@@ -14233,25 +14241,25 @@
         <v>96</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14273,10 +14281,10 @@
         <v>98</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14291,7 +14299,7 @@
         <v>74</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>74</v>
@@ -14327,7 +14335,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -14342,25 +14350,25 @@
         <v>96</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -14382,13 +14390,13 @@
         <v>98</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14402,7 +14410,7 @@
         <v>74</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>74</v>
@@ -14438,7 +14446,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -14453,21 +14461,21 @@
         <v>96</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14493,10 +14501,10 @@
         <v>98</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14573,10 +14581,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14680,13 +14688,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>74</v>
@@ -14708,13 +14716,13 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14774,13 +14782,13 @@
         <v>76</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>74</v>
+        <v>244</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>113</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>74</v>
+        <v>234</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>74</v>
@@ -14791,13 +14799,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>74</v>
@@ -14819,7 +14827,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="L111" t="s" s="2">
         <v>242</v>
@@ -14902,10 +14910,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15011,10 +15019,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15120,10 +15128,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15163,7 +15171,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>74</v>
@@ -15231,10 +15239,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15340,10 +15348,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15449,10 +15457,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15560,10 +15568,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15605,7 +15613,7 @@
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="S118" t="s" s="2">
         <v>74</v>
@@ -15673,10 +15681,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15784,10 +15792,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15895,10 +15903,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16006,10 +16014,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16119,10 +16127,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16148,10 +16156,10 @@
         <v>98</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16175,7 +16183,7 @@
         <v>74</v>
       </c>
       <c r="W123" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="X123" t="s" s="2">
         <v>74</v>
@@ -16202,7 +16210,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>75</v>
@@ -16228,14 +16236,14 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -16257,10 +16265,10 @@
         <v>98</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16311,7 +16319,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>75</v>
@@ -16326,25 +16334,25 @@
         <v>96</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -16366,10 +16374,10 @@
         <v>98</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -16384,7 +16392,7 @@
         <v>74</v>
       </c>
       <c r="T125" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="U125" t="s" s="2">
         <v>74</v>
@@ -16420,7 +16428,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>75</v>
@@ -16435,21 +16443,21 @@
         <v>96</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16475,13 +16483,13 @@
         <v>98</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -16531,7 +16539,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>75</v>
@@ -16546,21 +16554,21 @@
         <v>96</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16586,14 +16594,14 @@
         <v>347</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>74</v>
@@ -16606,7 +16614,7 @@
         <v>74</v>
       </c>
       <c r="T127" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="U127" t="s" s="2">
         <v>74</v>
@@ -16642,7 +16650,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>75</v>
@@ -16657,21 +16665,21 @@
         <v>96</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16777,10 +16785,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16888,10 +16896,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16914,16 +16922,16 @@
         <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -16973,7 +16981,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>75</v>
@@ -16982,27 +16990,27 @@
         <v>84</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17025,23 +17033,23 @@
         <v>85</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q131" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="R131" t="s" s="2">
         <v>74</v>
@@ -17086,7 +17094,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>75</v>
@@ -17095,27 +17103,27 @@
         <v>84</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17138,13 +17146,13 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17195,7 +17203,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>75</v>
@@ -17210,21 +17218,21 @@
         <v>96</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17247,17 +17255,17 @@
         <v>85</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>74</v>
@@ -17306,7 +17314,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>75</v>
@@ -17321,7 +17329,7 @@
         <v>96</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>74</v>
@@ -17332,10 +17340,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17361,14 +17369,14 @@
         <v>190</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>74</v>
@@ -17417,7 +17425,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>75</v>
@@ -17432,10 +17440,10 @@
         <v>96</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>74</v>
@@ -17443,10 +17451,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17469,13 +17477,13 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -17526,7 +17534,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>75</v>
@@ -17541,7 +17549,7 @@
         <v>96</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>74</v>
@@ -17552,10 +17560,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17661,10 +17669,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17772,14 +17780,14 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -17801,10 +17809,10 @@
         <v>105</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>108</v>
@@ -17859,7 +17867,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>75</v>
@@ -17885,10 +17893,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17911,13 +17919,13 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -17968,7 +17976,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>84</v>
@@ -17983,7 +17991,7 @@
         <v>96</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>74</v>
@@ -17994,10 +18002,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18023,10 +18031,10 @@
         <v>173</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18056,10 +18064,10 @@
         <v>314</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>74</v>
@@ -18077,7 +18085,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>75</v>
@@ -18092,7 +18100,7 @@
         <v>96</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>74</v>

--- a/docs/StructureDefinition-DIPSPerson.xlsx
+++ b/docs/StructureDefinition-DIPSPerson.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T19:39:02+00:00</t>
+    <t>2026-09-18T19:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPerson.xlsx
+++ b/docs/StructureDefinition-DIPSPerson.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T19:41:15+00:00</t>
+    <t>2026-09-29T03:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPerson.xlsx
+++ b/docs/StructureDefinition-DIPSPerson.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T03:57:01+00:00</t>
+    <t>2026-09-29T04:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
